--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2764,6 +2764,782 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128456990</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stensjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>577383</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7021294</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128456979</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stensjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>577145</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7021166</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128456994</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80170</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stensjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>577437</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7021280</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128456982</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stensjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>577145</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7021166</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128456996</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stensjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>577360</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7021223</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128456988</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91932</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>760</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stensjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>577369</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7021324</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128456980</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91358</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stensjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>577145</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7021166</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128456995</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stensjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>577437</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7021280</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -2866,7 +2866,7 @@
         <v>128456979</v>
       </c>
       <c r="B21" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>128456996</v>
       </c>
       <c r="B24" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>128456988</v>
       </c>
       <c r="B25" t="n">
-        <v>91932</v>
+        <v>91934</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>128456980</v>
       </c>
       <c r="B26" t="n">
-        <v>91358</v>
+        <v>91360</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2766,32 +2766,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128456990</v>
+        <v>128456979</v>
       </c>
       <c r="B20" t="n">
-        <v>80135</v>
+        <v>92742</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577383</v>
+        <v>577145</v>
       </c>
       <c r="R20" t="n">
-        <v>7021294</v>
+        <v>7021166</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2863,32 +2863,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128456979</v>
+        <v>128456990</v>
       </c>
       <c r="B21" t="n">
-        <v>92650</v>
+        <v>80188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577145</v>
+        <v>577383</v>
       </c>
       <c r="R21" t="n">
-        <v>7021166</v>
+        <v>7021294</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2963,7 +2963,7 @@
         <v>128456994</v>
       </c>
       <c r="B22" t="n">
-        <v>80170</v>
+        <v>80223</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>128456982</v>
       </c>
       <c r="B23" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>128456996</v>
       </c>
       <c r="B24" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>128456988</v>
       </c>
       <c r="B25" t="n">
-        <v>91934</v>
+        <v>92026</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>128456980</v>
       </c>
       <c r="B26" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>128456995</v>
       </c>
       <c r="B27" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3539,6 +3539,1211 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128585670</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>577380</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7021333</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128585673</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>577477</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7021305</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128585672</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>577464</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7021305</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128585671</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>577340</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7021313</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128585695</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>577453</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7021264</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128585692</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>577377</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7021326</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128585693</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>577363</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7021319</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128585684</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>577437</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7021282</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128585694</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>577363</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7021305</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128585682</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>577367</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7021320</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128585683</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>577382</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7021301</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128585674</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>577478</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7021310</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -3251,32 +3251,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128456988</v>
+        <v>128456980</v>
       </c>
       <c r="B25" t="n">
-        <v>92026</v>
+        <v>91452</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577369</v>
+        <v>577145</v>
       </c>
       <c r="R25" t="n">
-        <v>7021324</v>
+        <v>7021166</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3348,32 +3348,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128456980</v>
+        <v>128456988</v>
       </c>
       <c r="B26" t="n">
-        <v>91452</v>
+        <v>92026</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577145</v>
+        <v>577369</v>
       </c>
       <c r="R26" t="n">
-        <v>7021166</v>
+        <v>7021324</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -3251,32 +3251,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128456980</v>
+        <v>128456988</v>
       </c>
       <c r="B25" t="n">
-        <v>91452</v>
+        <v>92026</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577145</v>
+        <v>577369</v>
       </c>
       <c r="R25" t="n">
-        <v>7021166</v>
+        <v>7021324</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3348,32 +3348,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128456988</v>
+        <v>128456980</v>
       </c>
       <c r="B26" t="n">
-        <v>92026</v>
+        <v>91452</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577369</v>
+        <v>577145</v>
       </c>
       <c r="R26" t="n">
-        <v>7021324</v>
+        <v>7021166</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3545,7 +3545,7 @@
         <v>128585670</v>
       </c>
       <c r="B28" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>128585673</v>
       </c>
       <c r="B29" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>128585672</v>
       </c>
       <c r="B30" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>128585671</v>
       </c>
       <c r="B31" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>128585695</v>
       </c>
       <c r="B32" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>128585692</v>
       </c>
       <c r="B33" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128585693</v>
       </c>
       <c r="B34" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>128585684</v>
       </c>
       <c r="B35" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>128585694</v>
       </c>
       <c r="B36" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>128585682</v>
       </c>
       <c r="B37" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>128585683</v>
       </c>
       <c r="B38" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>128585674</v>
       </c>
       <c r="B39" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -2766,32 +2766,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128456979</v>
+        <v>128456990</v>
       </c>
       <c r="B20" t="n">
-        <v>92742</v>
+        <v>80192</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577145</v>
+        <v>577383</v>
       </c>
       <c r="R20" t="n">
-        <v>7021166</v>
+        <v>7021294</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2863,32 +2863,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128456990</v>
+        <v>128456979</v>
       </c>
       <c r="B21" t="n">
-        <v>80188</v>
+        <v>92754</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577383</v>
+        <v>577145</v>
       </c>
       <c r="R21" t="n">
-        <v>7021294</v>
+        <v>7021166</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2963,7 +2963,7 @@
         <v>128456994</v>
       </c>
       <c r="B22" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>128456982</v>
       </c>
       <c r="B23" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>128456996</v>
       </c>
       <c r="B24" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3251,32 +3251,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128456988</v>
+        <v>128456980</v>
       </c>
       <c r="B25" t="n">
-        <v>92026</v>
+        <v>91464</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577369</v>
+        <v>577145</v>
       </c>
       <c r="R25" t="n">
-        <v>7021324</v>
+        <v>7021166</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3348,32 +3348,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128456980</v>
+        <v>128456988</v>
       </c>
       <c r="B26" t="n">
-        <v>91452</v>
+        <v>92038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577145</v>
+        <v>577369</v>
       </c>
       <c r="R26" t="n">
-        <v>7021166</v>
+        <v>7021324</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3448,7 +3448,7 @@
         <v>128456995</v>
       </c>
       <c r="B27" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>128585695</v>
       </c>
       <c r="B32" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>128585692</v>
       </c>
       <c r="B33" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128585693</v>
       </c>
       <c r="B34" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>128585694</v>
       </c>
       <c r="B36" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -2769,7 +2769,7 @@
         <v>128456990</v>
       </c>
       <c r="B20" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>128456979</v>
       </c>
       <c r="B21" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>128456994</v>
       </c>
       <c r="B22" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>128456982</v>
       </c>
       <c r="B23" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>128456996</v>
       </c>
       <c r="B24" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3251,32 +3251,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128456980</v>
+        <v>128456988</v>
       </c>
       <c r="B25" t="n">
-        <v>91464</v>
+        <v>92040</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577145</v>
+        <v>577369</v>
       </c>
       <c r="R25" t="n">
-        <v>7021166</v>
+        <v>7021324</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3348,32 +3348,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128456988</v>
+        <v>128456980</v>
       </c>
       <c r="B26" t="n">
-        <v>92038</v>
+        <v>91466</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577369</v>
+        <v>577145</v>
       </c>
       <c r="R26" t="n">
-        <v>7021324</v>
+        <v>7021166</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3448,7 +3448,7 @@
         <v>128456995</v>
       </c>
       <c r="B27" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>128585695</v>
       </c>
       <c r="B32" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>128585692</v>
       </c>
       <c r="B33" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128585693</v>
       </c>
       <c r="B34" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>128585684</v>
       </c>
       <c r="B35" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>128585694</v>
       </c>
       <c r="B36" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>128585682</v>
       </c>
       <c r="B37" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>128585683</v>
       </c>
       <c r="B38" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -2766,32 +2766,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128456990</v>
+        <v>128456979</v>
       </c>
       <c r="B20" t="n">
-        <v>80194</v>
+        <v>92756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577383</v>
+        <v>577145</v>
       </c>
       <c r="R20" t="n">
-        <v>7021294</v>
+        <v>7021166</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2863,32 +2863,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128456979</v>
+        <v>128456990</v>
       </c>
       <c r="B21" t="n">
-        <v>92756</v>
+        <v>80194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577145</v>
+        <v>577383</v>
       </c>
       <c r="R21" t="n">
-        <v>7021166</v>
+        <v>7021294</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2960,32 +2960,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128456994</v>
+        <v>128456982</v>
       </c>
       <c r="B22" t="n">
-        <v>80229</v>
+        <v>80194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577437</v>
+        <v>577145</v>
       </c>
       <c r="R22" t="n">
-        <v>7021280</v>
+        <v>7021166</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3057,32 +3057,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128456982</v>
+        <v>128456994</v>
       </c>
       <c r="B23" t="n">
-        <v>80194</v>
+        <v>80229</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577145</v>
+        <v>577437</v>
       </c>
       <c r="R23" t="n">
-        <v>7021166</v>
+        <v>7021280</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
         <v>128585695</v>
       </c>
       <c r="B32" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>128585692</v>
       </c>
       <c r="B33" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128585693</v>
       </c>
       <c r="B34" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>128585694</v>
       </c>
       <c r="B36" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -2769,7 +2769,7 @@
         <v>128456979</v>
       </c>
       <c r="B20" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2960,32 +2960,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128456982</v>
+        <v>128456994</v>
       </c>
       <c r="B22" t="n">
-        <v>80194</v>
+        <v>80229</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577145</v>
+        <v>577437</v>
       </c>
       <c r="R22" t="n">
-        <v>7021166</v>
+        <v>7021280</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3057,32 +3057,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128456994</v>
+        <v>128456982</v>
       </c>
       <c r="B23" t="n">
-        <v>80229</v>
+        <v>80194</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577437</v>
+        <v>577145</v>
       </c>
       <c r="R23" t="n">
-        <v>7021280</v>
+        <v>7021166</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3157,7 +3157,7 @@
         <v>128456996</v>
       </c>
       <c r="B24" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3251,32 +3251,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128456988</v>
+        <v>128456980</v>
       </c>
       <c r="B25" t="n">
-        <v>92040</v>
+        <v>91467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577369</v>
+        <v>577145</v>
       </c>
       <c r="R25" t="n">
-        <v>7021324</v>
+        <v>7021166</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3348,32 +3348,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128456980</v>
+        <v>128456988</v>
       </c>
       <c r="B26" t="n">
-        <v>91466</v>
+        <v>92041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577145</v>
+        <v>577369</v>
       </c>
       <c r="R26" t="n">
-        <v>7021166</v>
+        <v>7021324</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
         <v>128585695</v>
       </c>
       <c r="B32" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>128585692</v>
       </c>
       <c r="B33" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128585693</v>
       </c>
       <c r="B34" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>128585694</v>
       </c>
       <c r="B36" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2766,32 +2766,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128456979</v>
+        <v>128456990</v>
       </c>
       <c r="B20" t="n">
-        <v>92757</v>
+        <v>80194</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577145</v>
+        <v>577383</v>
       </c>
       <c r="R20" t="n">
-        <v>7021166</v>
+        <v>7021294</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2863,32 +2863,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128456990</v>
+        <v>128456979</v>
       </c>
       <c r="B21" t="n">
-        <v>80194</v>
+        <v>92757</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577383</v>
+        <v>577145</v>
       </c>
       <c r="R21" t="n">
-        <v>7021294</v>
+        <v>7021166</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3545,7 +3545,7 @@
         <v>128585670</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>128585673</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>128585672</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>128585671</v>
       </c>
       <c r="B31" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>128585695</v>
       </c>
       <c r="B32" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>128585692</v>
       </c>
       <c r="B33" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128585693</v>
       </c>
       <c r="B34" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>128585684</v>
       </c>
       <c r="B35" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>128585694</v>
       </c>
       <c r="B36" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>128585682</v>
       </c>
       <c r="B37" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>128585683</v>
       </c>
       <c r="B38" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>128585674</v>
       </c>
       <c r="B39" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4744,6 +4744,212 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128821071</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92068</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>760</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>577374</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7021331</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128821170</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>577248</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7021217</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -2766,32 +2766,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128456990</v>
+        <v>128456979</v>
       </c>
       <c r="B20" t="n">
-        <v>80194</v>
+        <v>92784</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577383</v>
+        <v>577145</v>
       </c>
       <c r="R20" t="n">
-        <v>7021294</v>
+        <v>7021166</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2863,32 +2863,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128456979</v>
+        <v>128456990</v>
       </c>
       <c r="B21" t="n">
-        <v>92757</v>
+        <v>80221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577145</v>
+        <v>577383</v>
       </c>
       <c r="R21" t="n">
-        <v>7021166</v>
+        <v>7021294</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2963,7 +2963,7 @@
         <v>128456994</v>
       </c>
       <c r="B22" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>128456982</v>
       </c>
       <c r="B23" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>128456996</v>
       </c>
       <c r="B24" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3251,32 +3251,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128456980</v>
+        <v>128456988</v>
       </c>
       <c r="B25" t="n">
-        <v>91467</v>
+        <v>92068</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577145</v>
+        <v>577369</v>
       </c>
       <c r="R25" t="n">
-        <v>7021166</v>
+        <v>7021324</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3348,32 +3348,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128456988</v>
+        <v>128456980</v>
       </c>
       <c r="B26" t="n">
-        <v>92041</v>
+        <v>91494</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577369</v>
+        <v>577145</v>
       </c>
       <c r="R26" t="n">
-        <v>7021324</v>
+        <v>7021166</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3448,7 +3448,7 @@
         <v>128456995</v>
       </c>
       <c r="B27" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -2766,32 +2766,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128456979</v>
+        <v>128456990</v>
       </c>
       <c r="B20" t="n">
-        <v>92784</v>
+        <v>80221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577145</v>
+        <v>577383</v>
       </c>
       <c r="R20" t="n">
-        <v>7021166</v>
+        <v>7021294</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2863,32 +2863,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128456990</v>
+        <v>128456979</v>
       </c>
       <c r="B21" t="n">
-        <v>80221</v>
+        <v>92784</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577383</v>
+        <v>577145</v>
       </c>
       <c r="R21" t="n">
-        <v>7021294</v>
+        <v>7021166</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
         <v>128585695</v>
       </c>
       <c r="B32" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>128585692</v>
       </c>
       <c r="B33" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128585693</v>
       </c>
       <c r="B34" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>128585684</v>
       </c>
       <c r="B35" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>128585694</v>
       </c>
       <c r="B36" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>128585682</v>
       </c>
       <c r="B37" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>128585683</v>
       </c>
       <c r="B38" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>128821071</v>
       </c>
       <c r="B40" t="n">
-        <v>92068</v>
+        <v>92073</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -2766,32 +2766,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128456990</v>
+        <v>128456979</v>
       </c>
       <c r="B20" t="n">
-        <v>80221</v>
+        <v>92794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577383</v>
+        <v>577145</v>
       </c>
       <c r="R20" t="n">
-        <v>7021294</v>
+        <v>7021166</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2863,32 +2863,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128456979</v>
+        <v>128456990</v>
       </c>
       <c r="B21" t="n">
-        <v>92784</v>
+        <v>80225</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577145</v>
+        <v>577383</v>
       </c>
       <c r="R21" t="n">
-        <v>7021166</v>
+        <v>7021294</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2960,32 +2960,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128456994</v>
+        <v>128456982</v>
       </c>
       <c r="B22" t="n">
-        <v>80256</v>
+        <v>80225</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577437</v>
+        <v>577145</v>
       </c>
       <c r="R22" t="n">
-        <v>7021280</v>
+        <v>7021166</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3057,32 +3057,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128456982</v>
+        <v>128456994</v>
       </c>
       <c r="B23" t="n">
-        <v>80221</v>
+        <v>80260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577145</v>
+        <v>577437</v>
       </c>
       <c r="R23" t="n">
-        <v>7021166</v>
+        <v>7021280</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3157,7 +3157,7 @@
         <v>128456996</v>
       </c>
       <c r="B24" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3251,32 +3251,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128456988</v>
+        <v>128456980</v>
       </c>
       <c r="B25" t="n">
-        <v>92068</v>
+        <v>91504</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577369</v>
+        <v>577145</v>
       </c>
       <c r="R25" t="n">
-        <v>7021324</v>
+        <v>7021166</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3348,32 +3348,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128456980</v>
+        <v>128456988</v>
       </c>
       <c r="B26" t="n">
-        <v>91494</v>
+        <v>92078</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577145</v>
+        <v>577369</v>
       </c>
       <c r="R26" t="n">
-        <v>7021166</v>
+        <v>7021324</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3448,7 +3448,7 @@
         <v>128456995</v>
       </c>
       <c r="B27" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>128585695</v>
       </c>
       <c r="B32" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>128585692</v>
       </c>
       <c r="B33" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128585693</v>
       </c>
       <c r="B34" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>128585694</v>
       </c>
       <c r="B36" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>128821071</v>
       </c>
       <c r="B40" t="n">
-        <v>92073</v>
+        <v>92078</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -2766,32 +2766,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128456979</v>
+        <v>128456990</v>
       </c>
       <c r="B20" t="n">
-        <v>92794</v>
+        <v>80225</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577145</v>
+        <v>577383</v>
       </c>
       <c r="R20" t="n">
-        <v>7021166</v>
+        <v>7021294</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2863,32 +2863,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128456990</v>
+        <v>128456979</v>
       </c>
       <c r="B21" t="n">
-        <v>80225</v>
+        <v>92794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577383</v>
+        <v>577145</v>
       </c>
       <c r="R21" t="n">
-        <v>7021294</v>
+        <v>7021166</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2960,32 +2960,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128456982</v>
+        <v>128456994</v>
       </c>
       <c r="B22" t="n">
-        <v>80225</v>
+        <v>80260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577145</v>
+        <v>577437</v>
       </c>
       <c r="R22" t="n">
-        <v>7021166</v>
+        <v>7021280</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3057,32 +3057,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128456994</v>
+        <v>128456982</v>
       </c>
       <c r="B23" t="n">
-        <v>80260</v>
+        <v>80225</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577437</v>
+        <v>577145</v>
       </c>
       <c r="R23" t="n">
-        <v>7021280</v>
+        <v>7021166</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3251,32 +3251,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128456980</v>
+        <v>128456988</v>
       </c>
       <c r="B25" t="n">
-        <v>91504</v>
+        <v>92078</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577145</v>
+        <v>577369</v>
       </c>
       <c r="R25" t="n">
-        <v>7021166</v>
+        <v>7021324</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3348,32 +3348,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128456988</v>
+        <v>128456980</v>
       </c>
       <c r="B26" t="n">
-        <v>92078</v>
+        <v>91504</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577369</v>
+        <v>577145</v>
       </c>
       <c r="R26" t="n">
-        <v>7021324</v>
+        <v>7021166</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -2766,32 +2766,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128456990</v>
+        <v>128456979</v>
       </c>
       <c r="B20" t="n">
-        <v>80225</v>
+        <v>92794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577383</v>
+        <v>577145</v>
       </c>
       <c r="R20" t="n">
-        <v>7021294</v>
+        <v>7021166</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2863,32 +2863,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128456979</v>
+        <v>128456990</v>
       </c>
       <c r="B21" t="n">
-        <v>92794</v>
+        <v>80225</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577145</v>
+        <v>577383</v>
       </c>
       <c r="R21" t="n">
-        <v>7021166</v>
+        <v>7021294</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3545,7 +3545,7 @@
         <v>128585670</v>
       </c>
       <c r="B28" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>128585673</v>
       </c>
       <c r="B29" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>128585672</v>
       </c>
       <c r="B30" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>128585671</v>
       </c>
       <c r="B31" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>128585695</v>
       </c>
       <c r="B32" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>128585692</v>
       </c>
       <c r="B33" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128585693</v>
       </c>
       <c r="B34" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>128585684</v>
       </c>
       <c r="B35" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>128585694</v>
       </c>
       <c r="B36" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>128585682</v>
       </c>
       <c r="B37" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>128585683</v>
       </c>
       <c r="B38" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>128585674</v>
       </c>
       <c r="B39" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>128821071</v>
       </c>
       <c r="B40" t="n">
-        <v>92078</v>
+        <v>92082</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>128821170</v>
       </c>
       <c r="B41" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -2766,32 +2766,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128456979</v>
+        <v>128456990</v>
       </c>
       <c r="B20" t="n">
-        <v>92794</v>
+        <v>80229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577145</v>
+        <v>577383</v>
       </c>
       <c r="R20" t="n">
-        <v>7021166</v>
+        <v>7021294</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2863,32 +2863,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128456990</v>
+        <v>128456979</v>
       </c>
       <c r="B21" t="n">
-        <v>80225</v>
+        <v>92798</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577383</v>
+        <v>577145</v>
       </c>
       <c r="R21" t="n">
-        <v>7021294</v>
+        <v>7021166</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2963,7 +2963,7 @@
         <v>128456994</v>
       </c>
       <c r="B22" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>128456982</v>
       </c>
       <c r="B23" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>128456996</v>
       </c>
       <c r="B24" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>128456988</v>
       </c>
       <c r="B25" t="n">
-        <v>92078</v>
+        <v>92082</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>128456980</v>
       </c>
       <c r="B26" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>128456995</v>
       </c>
       <c r="B27" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128585670</v>
+        <v>128585673</v>
       </c>
       <c r="B28" t="n">
         <v>57720</v>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577380</v>
+        <v>577477</v>
       </c>
       <c r="R28" t="n">
-        <v>7021333</v>
+        <v>7021305</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3644,7 +3644,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128585673</v>
+        <v>128585670</v>
       </c>
       <c r="B29" t="n">
         <v>57720</v>
@@ -3684,10 +3684,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577477</v>
+        <v>577380</v>
       </c>
       <c r="R29" t="n">
-        <v>7021305</v>
+        <v>7021333</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -2769,7 +2769,7 @@
         <v>128456990</v>
       </c>
       <c r="B20" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>128456979</v>
       </c>
       <c r="B21" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>128456994</v>
       </c>
       <c r="B22" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>128456982</v>
       </c>
       <c r="B23" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>128456996</v>
       </c>
       <c r="B24" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3251,32 +3251,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128456988</v>
+        <v>128456980</v>
       </c>
       <c r="B25" t="n">
-        <v>92082</v>
+        <v>91513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577369</v>
+        <v>577145</v>
       </c>
       <c r="R25" t="n">
-        <v>7021324</v>
+        <v>7021166</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3348,32 +3348,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128456980</v>
+        <v>128456988</v>
       </c>
       <c r="B26" t="n">
-        <v>91508</v>
+        <v>92087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577145</v>
+        <v>577369</v>
       </c>
       <c r="R26" t="n">
-        <v>7021166</v>
+        <v>7021324</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3448,7 +3448,7 @@
         <v>128456995</v>
       </c>
       <c r="B27" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,10 +3542,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128585673</v>
+        <v>128585670</v>
       </c>
       <c r="B28" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577477</v>
+        <v>577380</v>
       </c>
       <c r="R28" t="n">
-        <v>7021305</v>
+        <v>7021333</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3644,10 +3644,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128585670</v>
+        <v>128585673</v>
       </c>
       <c r="B29" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,10 +3684,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577380</v>
+        <v>577477</v>
       </c>
       <c r="R29" t="n">
-        <v>7021333</v>
+        <v>7021305</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3749,7 +3749,7 @@
         <v>128585672</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>128585671</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>128585695</v>
       </c>
       <c r="B32" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>128585692</v>
       </c>
       <c r="B33" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128585693</v>
       </c>
       <c r="B34" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>128585684</v>
       </c>
       <c r="B35" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>128585694</v>
       </c>
       <c r="B36" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>128585682</v>
       </c>
       <c r="B37" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>128585683</v>
       </c>
       <c r="B38" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>128585674</v>
       </c>
       <c r="B39" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>128821071</v>
       </c>
       <c r="B40" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>128821170</v>
       </c>
       <c r="B41" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -3953,7 +3953,7 @@
         <v>128585695</v>
       </c>
       <c r="B32" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>128585692</v>
       </c>
       <c r="B33" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128585693</v>
       </c>
       <c r="B34" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>128585684</v>
       </c>
       <c r="B35" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>128585694</v>
       </c>
       <c r="B36" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>128585682</v>
       </c>
       <c r="B37" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>128585683</v>
       </c>
       <c r="B38" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -4750,7 +4750,7 @@
         <v>128821071</v>
       </c>
       <c r="B40" t="n">
-        <v>92095</v>
+        <v>92100</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -3953,7 +3953,7 @@
         <v>128585695</v>
       </c>
       <c r="B32" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>128585692</v>
       </c>
       <c r="B33" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>128585693</v>
       </c>
       <c r="B34" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>128585684</v>
       </c>
       <c r="B35" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>128585694</v>
       </c>
       <c r="B36" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>128585682</v>
       </c>
       <c r="B37" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>128585683</v>
       </c>
       <c r="B38" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>128821071</v>
       </c>
       <c r="B40" t="n">
-        <v>92100</v>
+        <v>92103</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -3542,7 +3542,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128585670</v>
+        <v>128585673</v>
       </c>
       <c r="B28" t="n">
         <v>57723</v>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577380</v>
+        <v>577477</v>
       </c>
       <c r="R28" t="n">
-        <v>7021333</v>
+        <v>7021305</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3644,7 +3644,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128585673</v>
+        <v>128585670</v>
       </c>
       <c r="B29" t="n">
         <v>57723</v>
@@ -3684,10 +3684,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577477</v>
+        <v>577380</v>
       </c>
       <c r="R29" t="n">
-        <v>7021305</v>
+        <v>7021333</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -4750,7 +4750,7 @@
         <v>128821071</v>
       </c>
       <c r="B40" t="n">
-        <v>92103</v>
+        <v>92110</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>128821170</v>
       </c>
       <c r="B41" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -4750,7 +4750,7 @@
         <v>128821071</v>
       </c>
       <c r="B40" t="n">
-        <v>92110</v>
+        <v>92117</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -4750,7 +4750,7 @@
         <v>128821071</v>
       </c>
       <c r="B40" t="n">
-        <v>92117</v>
+        <v>92119</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>128821170</v>
       </c>
       <c r="B41" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -4750,7 +4750,7 @@
         <v>128821071</v>
       </c>
       <c r="B40" t="n">
-        <v>92119</v>
+        <v>92134</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 39198-2025 artfynd.xlsx
+++ b/artfynd/A 39198-2025 artfynd.xlsx
@@ -4750,7 +4750,7 @@
         <v>128821071</v>
       </c>
       <c r="B40" t="n">
-        <v>92134</v>
+        <v>92135</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
